--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/66.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/66.xlsx
@@ -426,13 +426,13 @@
         <v>-3.705025988265489</v>
       </c>
       <c r="E2">
-        <v>-9.612313087400993</v>
+        <v>-9.464598793744795</v>
       </c>
       <c r="F2">
-        <v>-3.500614522085995</v>
+        <v>-4.144492078771008</v>
       </c>
       <c r="G2">
-        <v>-8.551477954250815</v>
+        <v>-9.004254646565858</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.713649451573501</v>
       </c>
       <c r="E3">
-        <v>-10.09258039828447</v>
+        <v>-9.694441492004104</v>
       </c>
       <c r="F3">
-        <v>-3.701815852184564</v>
+        <v>-3.866593039214635</v>
       </c>
       <c r="G3">
-        <v>-8.541248368534468</v>
+        <v>-8.874630235975694</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.861895057177712</v>
       </c>
       <c r="E4">
-        <v>-10.54885132540131</v>
+        <v>-10.90247986066029</v>
       </c>
       <c r="F4">
-        <v>-3.508992629997909</v>
+        <v>-3.567763640491728</v>
       </c>
       <c r="G4">
-        <v>-8.508510383696615</v>
+        <v>-9.174906648024209</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-4.127751903224176</v>
       </c>
       <c r="E5">
-        <v>-10.30860672234638</v>
+        <v>-10.88327913086776</v>
       </c>
       <c r="F5">
-        <v>-3.487419457726801</v>
+        <v>-3.632379611379701</v>
       </c>
       <c r="G5">
-        <v>-7.951163489432615</v>
+        <v>-8.982097165271515</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-4.473956310328782</v>
       </c>
       <c r="E6">
-        <v>-11.55841573524932</v>
+        <v>-12.62077309507874</v>
       </c>
       <c r="F6">
-        <v>-3.42786978187435</v>
+        <v>-3.750778164261834</v>
       </c>
       <c r="G6">
-        <v>-8.678367854225542</v>
+        <v>-9.279344428151596</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-4.847262285668634</v>
       </c>
       <c r="E7">
-        <v>-13.60509126233399</v>
+        <v>-12.40220176862453</v>
       </c>
       <c r="F7">
-        <v>-2.995010537378483</v>
+        <v>-3.166081659935025</v>
       </c>
       <c r="G7">
-        <v>-8.494328006606377</v>
+        <v>-9.638243980609525</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.19174165869353</v>
       </c>
       <c r="E8">
-        <v>-13.06773347963581</v>
+        <v>-12.92416273969663</v>
       </c>
       <c r="F8">
-        <v>-3.151429497314308</v>
+        <v>-3.272189725661823</v>
       </c>
       <c r="G8">
-        <v>-8.502121030805821</v>
+        <v>-8.767203033226345</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.447843729775266</v>
       </c>
       <c r="E9">
-        <v>-14.32907198736227</v>
+        <v>-13.65080167896741</v>
       </c>
       <c r="F9">
-        <v>-3.225994989077305</v>
+        <v>-3.062389113554792</v>
       </c>
       <c r="G9">
-        <v>-8.028441553955822</v>
+        <v>-9.578650850357105</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.557638424013851</v>
       </c>
       <c r="E10">
-        <v>-14.4888456073009</v>
+        <v>-14.12350190978407</v>
       </c>
       <c r="F10">
-        <v>-2.819096778985174</v>
+        <v>-2.930003577076389</v>
       </c>
       <c r="G10">
-        <v>-9.37494636223467</v>
+        <v>-9.726671962508998</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-5.480578407937452</v>
       </c>
       <c r="E11">
-        <v>-14.69681124762915</v>
+        <v>-15.31230332085567</v>
       </c>
       <c r="F11">
-        <v>-2.75218705875885</v>
+        <v>-2.695678319642076</v>
       </c>
       <c r="G11">
-        <v>-8.561297032320294</v>
+        <v>-9.702736718260068</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-5.19998236851935</v>
       </c>
       <c r="E12">
-        <v>-15.55291020183121</v>
+        <v>-15.38009004827649</v>
       </c>
       <c r="F12">
-        <v>-2.273214257683939</v>
+        <v>-2.506214955641175</v>
       </c>
       <c r="G12">
-        <v>-8.216990364599473</v>
+        <v>-9.315045351247097</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-4.725880860200384</v>
       </c>
       <c r="E13">
-        <v>-15.63190490242102</v>
+        <v>-16.47454976034629</v>
       </c>
       <c r="F13">
-        <v>-1.998673419578516</v>
+        <v>-2.467494578132118</v>
       </c>
       <c r="G13">
-        <v>-8.504653598143364</v>
+        <v>-8.984023902775371</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.102739122994638</v>
       </c>
       <c r="E14">
-        <v>-16.33524484292234</v>
+        <v>-17.59996159225852</v>
       </c>
       <c r="F14">
-        <v>-1.988083570701127</v>
+        <v>-1.898240498928298</v>
       </c>
       <c r="G14">
-        <v>-8.10644131740659</v>
+        <v>-9.014629896285934</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-3.40102605059515</v>
       </c>
       <c r="E15">
-        <v>-17.11284270020144</v>
+        <v>-17.41502777073328</v>
       </c>
       <c r="F15">
-        <v>-1.587587812265233</v>
+        <v>-1.833660147838646</v>
       </c>
       <c r="G15">
-        <v>-8.153636454614441</v>
+        <v>-8.52170290767061</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-2.700930136207009</v>
       </c>
       <c r="E16">
-        <v>-17.14038035064208</v>
+        <v>-18.0785126114931</v>
       </c>
       <c r="F16">
-        <v>-1.608833779412235</v>
+        <v>-1.654655750665492</v>
       </c>
       <c r="G16">
-        <v>-7.884906231009641</v>
+        <v>-7.640018556378672</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.084672490811042</v>
       </c>
       <c r="E17">
-        <v>-18.91781092712671</v>
+        <v>-19.50059836106983</v>
       </c>
       <c r="F17">
-        <v>-1.371169372977237</v>
+        <v>-1.615987560302811</v>
       </c>
       <c r="G17">
-        <v>-6.739056898411558</v>
+        <v>-7.411418765800918</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.618847100880112</v>
       </c>
       <c r="E18">
-        <v>-18.85440776254531</v>
+        <v>-20.35307000759175</v>
       </c>
       <c r="F18">
-        <v>-0.9726708083494928</v>
+        <v>-1.018863888199204</v>
       </c>
       <c r="G18">
-        <v>-6.255382884578498</v>
+        <v>-7.482112155246515</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-1.339789326827734</v>
       </c>
       <c r="E19">
-        <v>-19.7000685841597</v>
+        <v>-21.48291068708349</v>
       </c>
       <c r="F19">
-        <v>-1.017641217912672</v>
+        <v>-1.09045222751654</v>
       </c>
       <c r="G19">
-        <v>-5.364928898153031</v>
+        <v>-6.716786858568881</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-1.261806868331446</v>
       </c>
       <c r="E20">
-        <v>-21.08397929785177</v>
+        <v>-21.4500928359499</v>
       </c>
       <c r="F20">
-        <v>-1.102437047100244</v>
+        <v>-0.7440505172182601</v>
       </c>
       <c r="G20">
-        <v>-5.182987936405765</v>
+        <v>-6.283952892582409</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-1.377105085072048</v>
       </c>
       <c r="E21">
-        <v>-21.99414370323142</v>
+        <v>-22.75486393788393</v>
       </c>
       <c r="F21">
-        <v>-0.9883037579751252</v>
+        <v>-0.4948229302075841</v>
       </c>
       <c r="G21">
-        <v>-4.671204080398754</v>
+        <v>-5.66877407829288</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-1.654736892880151</v>
       </c>
       <c r="E22">
-        <v>-22.85522850731593</v>
+        <v>-22.83147213267169</v>
       </c>
       <c r="F22">
-        <v>-0.4881371768995892</v>
+        <v>-0.7462026157307332</v>
       </c>
       <c r="G22">
-        <v>-4.172232035628721</v>
+        <v>-5.937193110616987</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-2.057607600997402</v>
       </c>
       <c r="E23">
-        <v>-23.2595668945128</v>
+        <v>-23.49398787999386</v>
       </c>
       <c r="F23">
-        <v>-0.5862531539241767</v>
+        <v>-0.3113155278328124</v>
       </c>
       <c r="G23">
-        <v>-3.289779637771673</v>
+        <v>-4.652711373016385</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-2.543271142281782</v>
       </c>
       <c r="E24">
-        <v>-23.06827962395479</v>
+        <v>-24.61808645444387</v>
       </c>
       <c r="F24">
-        <v>-0.4029569852371189</v>
+        <v>0.04248516010727329</v>
       </c>
       <c r="G24">
-        <v>-3.34589007411678</v>
+        <v>-5.314350383404046</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-3.063791401663336</v>
       </c>
       <c r="E25">
-        <v>-24.57206810157792</v>
+        <v>-25.12951419497412</v>
       </c>
       <c r="F25">
-        <v>-0.2154195754477276</v>
+        <v>-0.06724784137417442</v>
       </c>
       <c r="G25">
-        <v>-3.073872478791484</v>
+        <v>-5.280099479254746</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-3.579430072576354</v>
       </c>
       <c r="E26">
-        <v>-24.97416036566699</v>
+        <v>-25.83297640427365</v>
       </c>
       <c r="F26">
-        <v>-0.3577736852514198</v>
+        <v>0.1887731867068604</v>
       </c>
       <c r="G26">
-        <v>-2.861073922072672</v>
+        <v>-5.072074729203562</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-4.056243988928646</v>
       </c>
       <c r="E27">
-        <v>-25.52851351131595</v>
+        <v>-26.1529312068116</v>
       </c>
       <c r="F27">
-        <v>-0.4558300198230057</v>
+        <v>-0.1607622374762106</v>
       </c>
       <c r="G27">
-        <v>-3.944261248703429</v>
+        <v>-4.986295183735507</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-4.465659604514607</v>
       </c>
       <c r="E28">
-        <v>-25.25169242370107</v>
+        <v>-26.3876691854732</v>
       </c>
       <c r="F28">
-        <v>-0.5025507697083006</v>
+        <v>-0.06719316912558965</v>
       </c>
       <c r="G28">
-        <v>-3.297595835789892</v>
+        <v>-5.713347263433627</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.7892088060547</v>
       </c>
       <c r="E29">
-        <v>-25.23542161659151</v>
+        <v>-26.2780348297475</v>
       </c>
       <c r="F29">
-        <v>-0.6435761781979025</v>
+        <v>0.1272561382727607</v>
       </c>
       <c r="G29">
-        <v>-3.448225657826731</v>
+        <v>-6.023737392104615</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-5.014022922536829</v>
       </c>
       <c r="E30">
-        <v>-24.80231836249792</v>
+        <v>-25.42023316931855</v>
       </c>
       <c r="F30">
-        <v>-0.6029522123972119</v>
+        <v>-0.1336994744267508</v>
       </c>
       <c r="G30">
-        <v>-3.771765273379704</v>
+        <v>-5.343966523798366</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-5.130732168698252</v>
       </c>
       <c r="E31">
-        <v>-24.97996586934482</v>
+        <v>-26.85128982590448</v>
       </c>
       <c r="F31">
-        <v>-0.7359656513669369</v>
+        <v>-0.5759515769029621</v>
       </c>
       <c r="G31">
-        <v>-3.694258781214287</v>
+        <v>-5.491514227938143</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-5.135120907555556</v>
       </c>
       <c r="E32">
-        <v>-24.60071975662445</v>
+        <v>-25.37104488464723</v>
       </c>
       <c r="F32">
-        <v>-0.9015248172252517</v>
+        <v>-0.5335060311835154</v>
       </c>
       <c r="G32">
-        <v>-3.772698847221779</v>
+        <v>-5.263649378470108</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.02630723530046</v>
       </c>
       <c r="E33">
-        <v>-24.95764502096101</v>
+        <v>-25.49179211558775</v>
       </c>
       <c r="F33">
-        <v>-0.8762678951138948</v>
+        <v>-0.6503547086550108</v>
       </c>
       <c r="G33">
-        <v>-4.154348468625579</v>
+        <v>-5.49566234149885</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.805763090064871</v>
       </c>
       <c r="E34">
-        <v>-23.89314116445195</v>
+        <v>-25.21508876829707</v>
       </c>
       <c r="F34">
-        <v>-1.087002905651283</v>
+        <v>-0.3994256549989846</v>
       </c>
       <c r="G34">
-        <v>-3.92758603082212</v>
+        <v>-5.710265145536566</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.481406615765992</v>
       </c>
       <c r="E35">
-        <v>-23.62902244642858</v>
+        <v>-24.08287063995131</v>
       </c>
       <c r="F35">
-        <v>-0.7464088792140303</v>
+        <v>-0.6960847311265576</v>
       </c>
       <c r="G35">
-        <v>-4.495443907173307</v>
+        <v>-5.613249608508223</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.066556384265726</v>
       </c>
       <c r="E36">
-        <v>-23.4977872696863</v>
+        <v>-24.61853930184463</v>
       </c>
       <c r="F36">
-        <v>-0.8335274505990515</v>
+        <v>-0.9148300544490173</v>
       </c>
       <c r="G36">
-        <v>-3.996816159139359</v>
+        <v>-5.347164510789302</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.579103589172445</v>
       </c>
       <c r="E37">
-        <v>-23.52684195891951</v>
+        <v>-24.22458017707334</v>
       </c>
       <c r="F37">
-        <v>-0.9632249348553701</v>
+        <v>-1.175430297532728</v>
       </c>
       <c r="G37">
-        <v>-3.798166874055392</v>
+        <v>-4.696327810496283</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.045769422747416</v>
       </c>
       <c r="E38">
-        <v>-22.92969020542405</v>
+        <v>-23.62474303849134</v>
       </c>
       <c r="F38">
-        <v>-0.9563362315336894</v>
+        <v>-0.9248234787963906</v>
       </c>
       <c r="G38">
-        <v>-3.502253761027637</v>
+        <v>-4.985599969172259</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.496458215643099</v>
       </c>
       <c r="E39">
-        <v>-23.09374776177393</v>
+        <v>-24.44378096141463</v>
       </c>
       <c r="F39">
-        <v>-1.105805188960027</v>
+        <v>-1.086858769723196</v>
       </c>
       <c r="G39">
-        <v>-3.505153798920039</v>
+        <v>-4.429325691662983</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-1.960125312797913</v>
       </c>
       <c r="E40">
-        <v>-23.21974802256335</v>
+        <v>-23.49999716500204</v>
       </c>
       <c r="F40">
-        <v>-1.29482868987004</v>
+        <v>-1.373603944774065</v>
       </c>
       <c r="G40">
-        <v>-3.63614877536346</v>
+        <v>-4.756288411303562</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.466187210638566</v>
       </c>
       <c r="E41">
-        <v>-22.61473936666458</v>
+        <v>-23.09432287797291</v>
       </c>
       <c r="F41">
-        <v>-1.268179282154577</v>
+        <v>-1.20668377127295</v>
       </c>
       <c r="G41">
-        <v>-3.242634158746912</v>
+        <v>-4.005622210273821</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.036800347243314</v>
       </c>
       <c r="E42">
-        <v>-21.9923640129464</v>
+        <v>-22.73667758626912</v>
       </c>
       <c r="F42">
-        <v>-1.13015256366311</v>
+        <v>-1.289041715194083</v>
       </c>
       <c r="G42">
-        <v>-3.214686533304385</v>
+        <v>-4.87581234745341</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.6874947470688627</v>
       </c>
       <c r="E43">
-        <v>-21.96993448118641</v>
+        <v>-22.41077689735911</v>
       </c>
       <c r="F43">
-        <v>-1.388016709215373</v>
+        <v>-1.247849489355072</v>
       </c>
       <c r="G43">
-        <v>-3.741659172245572</v>
+        <v>-4.400020742549354</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.4307549459892293</v>
       </c>
       <c r="E44">
-        <v>-21.49276464652418</v>
+        <v>-22.10747329374738</v>
       </c>
       <c r="F44">
-        <v>-1.522452455015705</v>
+        <v>-1.565806719776023</v>
       </c>
       <c r="G44">
-        <v>-3.250066333482576</v>
+        <v>-4.368348753375147</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.2680867412795573</v>
       </c>
       <c r="E45">
-        <v>-20.31048423802362</v>
+        <v>-21.61469833765471</v>
       </c>
       <c r="F45">
-        <v>-1.242825441057093</v>
+        <v>-1.207092984769933</v>
       </c>
       <c r="G45">
-        <v>-2.945913272607575</v>
+        <v>-4.056968771587917</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.1911673275452189</v>
       </c>
       <c r="E46">
-        <v>-20.25362471838331</v>
+        <v>-21.70411305693616</v>
       </c>
       <c r="F46">
-        <v>-1.611309769579202</v>
+        <v>-1.634868538514821</v>
       </c>
       <c r="G46">
-        <v>-3.582253093984125</v>
+        <v>-3.445438178482665</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.1864495979180289</v>
       </c>
       <c r="E47">
-        <v>-20.19013098432177</v>
+        <v>-20.81137421953803</v>
       </c>
       <c r="F47">
-        <v>-1.563228012051108</v>
+        <v>-1.64714825689392</v>
       </c>
       <c r="G47">
-        <v>-2.69088208644428</v>
+        <v>-3.7377163125083</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.2324393207629634</v>
       </c>
       <c r="E48">
-        <v>-20.00594436100779</v>
+        <v>-20.84491209803884</v>
       </c>
       <c r="F48">
-        <v>-1.531433614396857</v>
+        <v>-1.4335040200379</v>
       </c>
       <c r="G48">
-        <v>-2.655303653533732</v>
+        <v>-4.14702885243825</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.3048822211392195</v>
       </c>
       <c r="E49">
-        <v>-19.82186642107</v>
+        <v>-19.74832853165944</v>
       </c>
       <c r="F49">
-        <v>-1.463273887759708</v>
+        <v>-1.943728638118227</v>
       </c>
       <c r="G49">
-        <v>-2.964154378528959</v>
+        <v>-3.932422737854996</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.3801239129346602</v>
       </c>
       <c r="E50">
-        <v>-19.47860356281458</v>
+        <v>-19.40244821542759</v>
       </c>
       <c r="F50">
-        <v>-1.68062009853884</v>
+        <v>-1.553781310189582</v>
       </c>
       <c r="G50">
-        <v>-2.960737895532431</v>
+        <v>-3.286151279860631</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-0.4341649449576538</v>
       </c>
       <c r="E51">
-        <v>-18.99000838823099</v>
+        <v>-19.12665509141245</v>
       </c>
       <c r="F51">
-        <v>-1.445800305765056</v>
+        <v>-1.892999418370786</v>
       </c>
       <c r="G51">
-        <v>-2.44581895289973</v>
+        <v>-3.831219360719476</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.4485821659222788</v>
       </c>
       <c r="E52">
-        <v>-18.8930718736228</v>
+        <v>-18.64503829527468</v>
       </c>
       <c r="F52">
-        <v>-1.859097654043813</v>
+        <v>-1.693077915909542</v>
       </c>
       <c r="G52">
-        <v>-3.360188320300892</v>
+        <v>-3.924215895463143</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.4138567152276897</v>
       </c>
       <c r="E53">
-        <v>-17.64583503395622</v>
+        <v>-18.58361407383464</v>
       </c>
       <c r="F53">
-        <v>-1.953218415084699</v>
+        <v>-1.870783432995106</v>
       </c>
       <c r="G53">
-        <v>-2.87307464965253</v>
+        <v>-3.38495451148018</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.3292257676573732</v>
       </c>
       <c r="E54">
-        <v>-17.67054238814207</v>
+        <v>-18.89318055699898</v>
       </c>
       <c r="F54">
-        <v>-1.958857111995555</v>
+        <v>-1.830571165793606</v>
       </c>
       <c r="G54">
-        <v>-3.08683988566881</v>
+        <v>-4.424197656622652</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-0.2032502050177189</v>
       </c>
       <c r="E55">
-        <v>-17.20076755153437</v>
+        <v>-17.82875821302206</v>
       </c>
       <c r="F55">
-        <v>-2.072629232933053</v>
+        <v>-1.992397708134907</v>
       </c>
       <c r="G55">
-        <v>-2.788569664217094</v>
+        <v>-4.763194209298482</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-0.05220782660987677</v>
       </c>
       <c r="E56">
-        <v>-16.76098479827946</v>
+        <v>-17.94031264172701</v>
       </c>
       <c r="F56">
-        <v>-1.917139701223169</v>
+        <v>-2.038920478210933</v>
       </c>
       <c r="G56">
-        <v>-2.880255222927209</v>
+        <v>-3.976393403707596</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.1027581205365322</v>
       </c>
       <c r="E57">
-        <v>-17.22211477800652</v>
+        <v>-16.40748306029269</v>
       </c>
       <c r="F57">
-        <v>-2.208584204550119</v>
+        <v>-2.474771785765712</v>
       </c>
       <c r="G57">
-        <v>-2.864374535975325</v>
+        <v>-4.191039244837322</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.238774071126347</v>
       </c>
       <c r="E58">
-        <v>-17.00623336511286</v>
+        <v>-16.06739919079066</v>
       </c>
       <c r="F58">
-        <v>-2.285770650775574</v>
+        <v>-2.032763223305924</v>
       </c>
       <c r="G58">
-        <v>-3.09555986261925</v>
+        <v>-4.579690670056681</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.332404485268237</v>
       </c>
       <c r="E59">
-        <v>-16.06839545507234</v>
+        <v>-16.65233764988743</v>
       </c>
       <c r="F59">
-        <v>-1.917764290244879</v>
+        <v>-2.364476322817763</v>
       </c>
       <c r="G59">
-        <v>-3.393439439697332</v>
+        <v>-5.165991595607147</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.3627053726286707</v>
       </c>
       <c r="E60">
-        <v>-15.92062229125405</v>
+        <v>-16.42912010910134</v>
       </c>
       <c r="F60">
-        <v>-2.335612689034618</v>
+        <v>-2.227836291358582</v>
       </c>
       <c r="G60">
-        <v>-3.130893315159891</v>
+        <v>-4.90115457355653</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>0.3154784444106304</v>
       </c>
       <c r="E61">
-        <v>-16.26612221566926</v>
+        <v>-15.74655227887321</v>
       </c>
       <c r="F61">
-        <v>-2.342470742762394</v>
+        <v>-2.452254274655413</v>
       </c>
       <c r="G61">
-        <v>-3.341781687102545</v>
+        <v>-4.867168513050372</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>0.1817795793383615</v>
       </c>
       <c r="E62">
-        <v>-15.45922513156053</v>
+        <v>-16.14515308950236</v>
       </c>
       <c r="F62">
-        <v>-2.497840989566275</v>
+        <v>-2.309378293387957</v>
       </c>
       <c r="G62">
-        <v>-3.769428028228979</v>
+        <v>-5.525996870275192</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-0.03841027945430576</v>
       </c>
       <c r="E63">
-        <v>-14.80208921135947</v>
+        <v>-15.27321806169547</v>
       </c>
       <c r="F63">
-        <v>-2.292454747348763</v>
+        <v>-2.59597104883671</v>
       </c>
       <c r="G63">
-        <v>-4.477037273974959</v>
+        <v>-5.414772471792298</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-0.3353913211568778</v>
       </c>
       <c r="E64">
-        <v>-15.78592283189589</v>
+        <v>-14.80394588570261</v>
       </c>
       <c r="F64">
-        <v>-2.27617070094453</v>
+        <v>-2.300113832355047</v>
       </c>
       <c r="G64">
-        <v>-4.21353109123113</v>
+        <v>-5.747475677397974</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-0.6940657515557608</v>
       </c>
       <c r="E65">
-        <v>-15.0925183633674</v>
+        <v>-14.01034892975441</v>
       </c>
       <c r="F65">
-        <v>-2.420354674341007</v>
+        <v>-2.4700931666747</v>
       </c>
       <c r="G65">
-        <v>-4.571930751312629</v>
+        <v>-5.767782563735863</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.092831866287843</v>
       </c>
       <c r="E66">
-        <v>-14.93977293508868</v>
+        <v>-15.4194153165591</v>
       </c>
       <c r="F66">
-        <v>-2.418139619905921</v>
+        <v>-2.625748371865144</v>
       </c>
       <c r="G66">
-        <v>-4.348634454688787</v>
+        <v>-6.086223939158359</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-1.505941371768795</v>
       </c>
       <c r="E67">
-        <v>-14.88914006720892</v>
+        <v>-14.87377042642688</v>
       </c>
       <c r="F67">
-        <v>-2.525608693275518</v>
+        <v>-2.44098267940552</v>
       </c>
       <c r="G67">
-        <v>-5.069876526965486</v>
+        <v>-5.988423802837209</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-1.909519718346189</v>
       </c>
       <c r="E68">
-        <v>-14.48738743867043</v>
+        <v>-14.64408169628384</v>
       </c>
       <c r="F68">
-        <v>-2.531186090998567</v>
+        <v>-2.613708880032856</v>
       </c>
       <c r="G68">
-        <v>-4.894586451206616</v>
+        <v>-6.261265724001784</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.281454577918026</v>
       </c>
       <c r="E69">
-        <v>-14.6310125202977</v>
+        <v>-15.36459813869625</v>
       </c>
       <c r="F69">
-        <v>-2.72646459416712</v>
+        <v>-2.65835788304375</v>
       </c>
       <c r="G69">
-        <v>-4.953884942906042</v>
+        <v>-7.07368684152109</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.603349820351951</v>
       </c>
       <c r="E70">
-        <v>-14.47021093675933</v>
+        <v>-13.68661285142007</v>
       </c>
       <c r="F70">
-        <v>-2.51871501974942</v>
+        <v>-2.72558900982236</v>
       </c>
       <c r="G70">
-        <v>-5.195352823994943</v>
+        <v>-7.086399336391891</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.865770566194701</v>
       </c>
       <c r="E71">
-        <v>-14.99212209461735</v>
+        <v>-14.67005702319183</v>
       </c>
       <c r="F71">
-        <v>-2.689969211501981</v>
+        <v>-2.749100561816018</v>
       </c>
       <c r="G71">
-        <v>-5.149776543555797</v>
+        <v>-5.920130558907584</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.065554704873284</v>
       </c>
       <c r="E72">
-        <v>-14.74397077594503</v>
+        <v>-14.47139739694934</v>
       </c>
       <c r="F72">
-        <v>-2.5486538744214</v>
+        <v>-2.949706295751975</v>
       </c>
       <c r="G72">
-        <v>-5.129708016496735</v>
+        <v>-6.607866599781319</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.204426484206659</v>
       </c>
       <c r="E73">
-        <v>-14.09079727050068</v>
+        <v>-14.95104430689377</v>
       </c>
       <c r="F73">
-        <v>-2.856658270497715</v>
+        <v>-2.895741472929198</v>
       </c>
       <c r="G73">
-        <v>-4.257981786186924</v>
+        <v>-6.321411715359262</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.29190116860192</v>
       </c>
       <c r="E74">
-        <v>-16.12353868306375</v>
+        <v>-15.17681137854618</v>
       </c>
       <c r="F74">
-        <v>-2.880627081297718</v>
+        <v>-2.787503674609804</v>
       </c>
       <c r="G74">
-        <v>-4.762181182363466</v>
+        <v>-6.857984936364336</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.339226747811606</v>
       </c>
       <c r="E75">
-        <v>-15.53564313043997</v>
+        <v>-15.04089828815397</v>
       </c>
       <c r="F75">
-        <v>-3.100003620581111</v>
+        <v>-3.002473299310303</v>
       </c>
       <c r="G75">
-        <v>-4.397385548300095</v>
+        <v>-7.087279941505337</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.356870118789038</v>
       </c>
       <c r="E76">
-        <v>-15.80775007661286</v>
+        <v>-15.83392012790319</v>
       </c>
       <c r="F76">
-        <v>-3.081456474432431</v>
+        <v>-3.300120617749416</v>
       </c>
       <c r="G76">
-        <v>-4.210710506431671</v>
+        <v>-5.90593162908965</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.35812123608722</v>
       </c>
       <c r="E77">
-        <v>-15.64771380518179</v>
+        <v>-15.74171586863302</v>
       </c>
       <c r="F77">
-        <v>-3.029315716630618</v>
+        <v>-2.997799650423709</v>
       </c>
       <c r="G77">
-        <v>-3.86099771784522</v>
+        <v>-6.55099473796218</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.35243359047004</v>
       </c>
       <c r="E78">
-        <v>-16.06464135011999</v>
+        <v>-15.65631337732236</v>
       </c>
       <c r="F78">
-        <v>-3.233152911804896</v>
+        <v>-3.185581428596926</v>
       </c>
       <c r="G78">
-        <v>-4.564342980936619</v>
+        <v>-6.082201626328144</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.345695294772094</v>
       </c>
       <c r="E79">
-        <v>-17.90395805239343</v>
+        <v>-17.14102792242518</v>
       </c>
       <c r="F79">
-        <v>-3.208155268690615</v>
+        <v>-3.420838599359388</v>
       </c>
       <c r="G79">
-        <v>-3.803675621832739</v>
+        <v>-6.673249874181925</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.343941496110003</v>
       </c>
       <c r="E80">
-        <v>-16.71404263671595</v>
+        <v>-17.44800864693114</v>
       </c>
       <c r="F80">
-        <v>-3.33386582063726</v>
+        <v>-3.187799796501623</v>
       </c>
       <c r="G80">
-        <v>-3.695298292513618</v>
+        <v>-4.713128829108084</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.347832938686002</v>
       </c>
       <c r="E81">
-        <v>-17.60624258570716</v>
+        <v>-17.71788305541826</v>
       </c>
       <c r="F81">
-        <v>-3.271384552546301</v>
+        <v>-3.075716716698433</v>
       </c>
       <c r="G81">
-        <v>-3.822449725585946</v>
+        <v>-5.106047547527563</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.355792209742555</v>
       </c>
       <c r="E82">
-        <v>-19.3546954570167</v>
+        <v>-19.02358702299787</v>
       </c>
       <c r="F82">
-        <v>-3.271653771952211</v>
+        <v>-3.520663498335951</v>
       </c>
       <c r="G82">
-        <v>-3.580157518657766</v>
+        <v>-5.221638555576757</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-3.370168085319404</v>
       </c>
       <c r="E83">
-        <v>-19.95620813098155</v>
+        <v>-19.66000064613983</v>
       </c>
       <c r="F83">
-        <v>-3.248208489350777</v>
+        <v>-3.231540908839048</v>
       </c>
       <c r="G83">
-        <v>-3.923666344903623</v>
+        <v>-4.996610843635875</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-3.39057837242194</v>
       </c>
       <c r="E84">
-        <v>-20.69767329415345</v>
+        <v>-20.5270811498105</v>
       </c>
       <c r="F84">
-        <v>-3.343016795335986</v>
+        <v>-3.435031846438955</v>
       </c>
       <c r="G84">
-        <v>-3.10278347298594</v>
+        <v>-4.958337626656362</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.417032725203768</v>
       </c>
       <c r="E85">
-        <v>-21.33009733169465</v>
+        <v>-21.18715152116853</v>
       </c>
       <c r="F85">
-        <v>-3.507405478054145</v>
+        <v>-3.787962748606101</v>
       </c>
       <c r="G85">
-        <v>-3.733243765484745</v>
+        <v>-5.544413435110157</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.453508714344253</v>
       </c>
       <c r="E86">
-        <v>-22.40128974431304</v>
+        <v>-23.0378165793052</v>
       </c>
       <c r="F86">
-        <v>-3.528372285386403</v>
+        <v>-3.272522729357748</v>
       </c>
       <c r="G86">
-        <v>-3.367987965591415</v>
+        <v>-4.599047429824799</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.49931366194357</v>
       </c>
       <c r="E87">
-        <v>-23.83189808197222</v>
+        <v>-24.09174644900635</v>
       </c>
       <c r="F87">
-        <v>-3.434152120257182</v>
+        <v>-3.780398097483736</v>
       </c>
       <c r="G87">
-        <v>-2.966243332764239</v>
+        <v>-4.518379366669378</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.553045772017715</v>
       </c>
       <c r="E88">
-        <v>-25.49922786990835</v>
+        <v>-24.53074577625793</v>
       </c>
       <c r="F88">
-        <v>-3.411365389740973</v>
+        <v>-3.608071998311952</v>
       </c>
       <c r="G88">
-        <v>-3.440224069258313</v>
+        <v>-5.201017167412636</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.617505993837153</v>
       </c>
       <c r="E89">
-        <v>-27.30019745428484</v>
+        <v>-27.22637879948581</v>
       </c>
       <c r="F89">
-        <v>-3.683450118497096</v>
+        <v>-3.44479498464835</v>
       </c>
       <c r="G89">
-        <v>-2.699542473575013</v>
+        <v>-4.760529220139369</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.691473894567533</v>
       </c>
       <c r="E90">
-        <v>-28.58205900621407</v>
+        <v>-28.43186310880166</v>
       </c>
       <c r="F90">
-        <v>-3.617849218767195</v>
+        <v>-3.58510385533453</v>
       </c>
       <c r="G90">
-        <v>-2.69369605015266</v>
+        <v>-5.460219640955413</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.774097451674741</v>
       </c>
       <c r="E91">
-        <v>-29.61740854706175</v>
+        <v>-30.14405648873179</v>
       </c>
       <c r="F91">
-        <v>-3.585629040267905</v>
+        <v>-3.569169379974279</v>
       </c>
       <c r="G91">
-        <v>-3.374148890839999</v>
+        <v>-4.933852831847912</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.870178005309335</v>
       </c>
       <c r="E92">
-        <v>-31.67315460758379</v>
+        <v>-32.19857533279774</v>
       </c>
       <c r="F92">
-        <v>-3.556155728076299</v>
+        <v>-3.492389662143598</v>
       </c>
       <c r="G92">
-        <v>-2.581163986181754</v>
+        <v>-5.3312738922008</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.979962234792603</v>
       </c>
       <c r="E93">
-        <v>-34.07041327115728</v>
+        <v>-33.9462108145489</v>
       </c>
       <c r="F93">
-        <v>-3.479937643344716</v>
+        <v>-3.212634251237552</v>
       </c>
       <c r="G93">
-        <v>-4.21094224461942</v>
+        <v>-6.68608485923768</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.103578098489482</v>
       </c>
       <c r="E94">
-        <v>-35.98025189915217</v>
+        <v>-35.80330857001346</v>
       </c>
       <c r="F94">
-        <v>-3.491978791911809</v>
+        <v>-3.536573122674118</v>
       </c>
       <c r="G94">
-        <v>-3.611471968913733</v>
+        <v>-6.131720766504563</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.246129853046763</v>
       </c>
       <c r="E95">
-        <v>-37.71255170367635</v>
+        <v>-38.13515569078317</v>
       </c>
       <c r="F95">
-        <v>-3.255624034340638</v>
+        <v>-3.503494755545528</v>
       </c>
       <c r="G95">
-        <v>-3.778449264823493</v>
+        <v>-6.324060151790679</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.405017541662315</v>
       </c>
       <c r="E96">
-        <v>-40.33701749363669</v>
+        <v>-40.20291126437354</v>
       </c>
       <c r="F96">
-        <v>-3.433740421657991</v>
+        <v>-3.257390113643407</v>
       </c>
       <c r="G96">
-        <v>-4.321044368164501</v>
+        <v>-6.792343439411667</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.576816265061143</v>
       </c>
       <c r="E97">
-        <v>-41.89758624260499</v>
+        <v>-41.82582125076843</v>
       </c>
       <c r="F97">
-        <v>-3.112958458393493</v>
+        <v>-2.951333209331073</v>
       </c>
       <c r="G97">
-        <v>-4.748048463456317</v>
+        <v>-6.389158719274908</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.755958304513457</v>
       </c>
       <c r="E98">
-        <v>-44.78201361144965</v>
+        <v>-44.35731067664029</v>
       </c>
       <c r="F98">
-        <v>-3.211950848130242</v>
+        <v>-2.914719370127335</v>
       </c>
       <c r="G98">
-        <v>-4.424465810811333</v>
+        <v>-6.893089961262768</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.930899902280869</v>
       </c>
       <c r="E99">
-        <v>-47.10475623522693</v>
+        <v>-47.2851593185075</v>
       </c>
       <c r="F99">
-        <v>-3.217892727510523</v>
+        <v>-3.115194222013649</v>
       </c>
       <c r="G99">
-        <v>-5.692374957442344</v>
+        <v>-7.350845714068874</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.079246442601108</v>
       </c>
       <c r="E100">
-        <v>-48.93004598926161</v>
+        <v>-49.19402206035374</v>
       </c>
       <c r="F100">
-        <v>-3.19707833978038</v>
+        <v>-3.055937788221789</v>
       </c>
       <c r="G100">
-        <v>-5.876325420331947</v>
+        <v>-7.657723353922695</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.188896163530033</v>
       </c>
       <c r="E101">
-        <v>-51.27905942287589</v>
+        <v>-51.24341693608002</v>
       </c>
       <c r="F101">
-        <v>-3.111596622383291</v>
+        <v>-2.651974483837777</v>
       </c>
       <c r="G101">
-        <v>-5.753481007006211</v>
+        <v>-8.346022187538107</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.22263781837663</v>
       </c>
       <c r="E102">
-        <v>-53.91626720657531</v>
+        <v>-52.80074329765883</v>
       </c>
       <c r="F102">
-        <v>-2.958597991453625</v>
+        <v>-2.870906189825866</v>
       </c>
       <c r="G102">
-        <v>-6.946661209179254</v>
+        <v>-8.836350397905102</v>
       </c>
     </row>
   </sheetData>
